--- a/data/trans_bre/DC-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/DC-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,54</t>
+          <t>1,65; 9,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,71</t>
+          <t>9,46; 17,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,92</t>
+          <t>5,11; 13,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 18,12</t>
+          <t>4,94; 17,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 71,55</t>
+          <t>8,72; 69,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,49; 169,2</t>
+          <t>62,97; 159,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,35; 165,25</t>
+          <t>41,47; 157,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,89; 91,02</t>
+          <t>24,25; 88,29</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,97</t>
+          <t>7,49; 14,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 13,78</t>
+          <t>7,09; 14,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,52</t>
+          <t>5,24; 11,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,28; 32,03</t>
+          <t>17,97; 31,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,64; 115,58</t>
+          <t>44,81; 112,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,5; 139,42</t>
+          <t>50,85; 135,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,88; 152,48</t>
+          <t>51,7; 147,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,04; 387,71</t>
+          <t>89,44; 361,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 18,2</t>
+          <t>8,82; 18,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,49</t>
+          <t>11,51; 19,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,22</t>
+          <t>2,91; 9,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 52,38</t>
+          <t>15,06; 53,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 95,57</t>
+          <t>37,49; 98,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122,11; 323,57</t>
+          <t>123,04; 301,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,33; 135,21</t>
+          <t>29,02; 132,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,81; 262,66</t>
+          <t>62,42; 268,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 14,03</t>
+          <t>6,7; 13,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 18,29</t>
+          <t>11,7; 18,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,45</t>
+          <t>7,22; 14,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 29,91</t>
+          <t>12,31; 28,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 81,74</t>
+          <t>32,52; 82,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,06; 217,21</t>
+          <t>102,79; 217,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,76; 155,73</t>
+          <t>57,96; 154,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,96; 132,06</t>
+          <t>49,53; 134,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,38</t>
+          <t>8,41; 12,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,19</t>
+          <t>11,77; 15,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,48</t>
+          <t>7,4; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,76; 32,93</t>
+          <t>16,58; 32,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,37; 75,35</t>
+          <t>45,17; 74,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>103,9; 159,46</t>
+          <t>105,42; 160,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,34; 121,69</t>
+          <t>71,56; 121,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,87; 186,06</t>
+          <t>78,21; 180,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DC-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/DC-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>16,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,81</t>
+          <t>1,79; 10,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 17,57</t>
+          <t>9,25; 17,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,07</t>
+          <t>5,42; 13,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 17,99</t>
+          <t>11,74; 20,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 69,87</t>
+          <t>9,35; 72,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,97; 159,67</t>
+          <t>67,62; 162,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,47; 157,45</t>
+          <t>47,87; 162,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,25; 88,29</t>
+          <t>47,28; 105,74</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>19,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>153,55%</t>
+          <t>104,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 14,9</t>
+          <t>7,71; 14,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,08</t>
+          <t>7,1; 13,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,31</t>
+          <t>5,44; 11,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 31,26</t>
+          <t>15,79; 23,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,81; 112,92</t>
+          <t>46,38; 117,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,85; 135,18</t>
+          <t>54,98; 138,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,7; 147,63</t>
+          <t>52,03; 145,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,44; 361,69</t>
+          <t>74,87; 140,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,91</t>
+          <t>18,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>130,52%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,74</t>
+          <t>8,63; 17,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 19,32</t>
+          <t>12,08; 19,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,38</t>
+          <t>2,96; 9,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,06; 53,91</t>
+          <t>13,95; 23,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,49; 98,84</t>
+          <t>36,57; 95,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123,04; 301,92</t>
+          <t>125,98; 311,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,02; 132,89</t>
+          <t>29,06; 138,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,42; 268,53</t>
+          <t>52,92; 113,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,18</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,8</t>
+          <t>6,73; 13,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 18,23</t>
+          <t>11,65; 18,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,09</t>
+          <t>7,5; 14,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 28,91</t>
+          <t>10,93; 18,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,52; 82,01</t>
+          <t>32,11; 82,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>102,79; 217,69</t>
+          <t>102,44; 224,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,96; 154,52</t>
+          <t>59,11; 151,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,53; 134,28</t>
+          <t>44,8; 92,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,16</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>109,71%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,31</t>
+          <t>8,42; 12,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 15,3</t>
+          <t>11,67; 15,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,77</t>
+          <t>7,18; 10,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,58; 32,31</t>
+          <t>15,32; 19,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,17; 74,5</t>
+          <t>45,86; 73,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>105,42; 160,14</t>
+          <t>104,6; 158,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,56; 121,28</t>
+          <t>69,92; 122,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,21; 180,52</t>
+          <t>67,67; 94,67</t>
         </is>
       </c>
     </row>
